--- a/docs/design-vi/demo/購読者Excelデータ取込_テンプレート-v3.xlsx
+++ b/docs/design-vi/demo/購読者Excelデータ取込_テンプレート-v3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11580"/>
+    <workbookView windowWidth="15210" windowHeight="9705"/>
   </bookViews>
   <sheets>
     <sheet name="購読者" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -266,13 +266,10 @@
     <t>備考</t>
   </si>
   <si>
-    <t>113-9002-001</t>
-  </si>
-  <si>
-    <t>MHV-002</t>
-  </si>
-  <si>
-    <t>松本松QA-1</t>
+    <t>116-5741-000</t>
+  </si>
+  <si>
+    <t>500</t>
   </si>
   <si>
     <t>一郎</t>
@@ -284,13 +281,13 @@
     <t>いちろう</t>
   </si>
   <si>
-    <t>DMT001</t>
-  </si>
-  <si>
-    <t>vqa.test14@gmail.com</t>
-  </si>
-  <si>
-    <t>3900874</t>
+    <t>001</t>
+  </si>
+  <si>
+    <t>vuquanganh412002.test1234@gmail.com</t>
+  </si>
+  <si>
+    <t>1111111</t>
   </si>
   <si>
     <t>20</t>
@@ -302,22 +299,16 @@
     <t>大手1-1-1</t>
   </si>
   <si>
-    <t>0263321111</t>
-  </si>
-  <si>
-    <t>DM001</t>
+    <t>09478542658</t>
+  </si>
+  <si>
+    <t>9999999999</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>SCR-011 検証用サンプル1（紙版・配達先=購読者情報と同じ）</t>
-  </si>
-  <si>
-    <t>vqa.test13@gmail.com</t>
+    <t>2026-08-22</t>
   </si>
 </sst>
 </file>
@@ -962,6 +953,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1355,7 +1347,7 @@
     <col min="5" max="6" width="17" customWidth="1"/>
     <col min="7" max="8" width="17.4285714285714" customWidth="1"/>
     <col min="9" max="10" width="10.8571428571429" customWidth="1"/>
-    <col min="11" max="11" width="29.1428571428571" customWidth="1"/>
+    <col min="11" max="11" width="43.8571428571429" customWidth="1"/>
     <col min="12" max="12" width="19.5714285714286" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="6.14285714285714" customWidth="1"/>
@@ -1432,7 +1424,7 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -1513,7 +1505,7 @@
       <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AV1" s="1" t="s">
@@ -1530,30 +1522,30 @@
       <c r="B2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>51</v>
       </c>
+      <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="M2">
         <v>1976</v>
@@ -1562,26 +1554,26 @@
         <v>1</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="V2" s="4"/>
       <c r="AH2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI2" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="AI2" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="AJ2">
         <v>2</v>
@@ -1590,98 +1582,45 @@
         <v>1</v>
       </c>
       <c r="AQ2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AU2" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX2" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="AX2" s="4"/>
     </row>
     <row r="3" customFormat="1" spans="1:50">
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
+      <c r="B3" s="4"/>
       <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="M3">
-        <v>1976</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="5"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="T3" s="4"/>
       <c r="V3" s="4"/>
-      <c r="AH3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ3">
-        <v>2</v>
-      </c>
-      <c r="AK3">
-        <v>1</v>
-      </c>
-      <c r="AQ3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU3" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="AW3" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX3" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4"/>
+      <c r="AJ3"/>
+      <c r="AK3"/>
+      <c r="AQ3" s="4"/>
+      <c r="AU3" s="4"/>
+      <c r="AW3" s="4"/>
+      <c r="AX3" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1" display="vqa.test14@gmail.com" tooltip="mailto:vqa.test14@gmail.com"/>
-    <hyperlink ref="K3" r:id="rId2" display="vqa.test13@gmail.com" tooltip="mailto:vqa.test13@gmail.com"/>
+    <hyperlink ref="K2" r:id="rId1" display="vuquanganh412002.test1234@gmail.com" tooltip="mailto:vuquanganh412002.test1234@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
